--- a/data/S1967_68_FINAL.xlsx
+++ b/data/S1967_68_FINAL.xlsx
@@ -26,8 +26,11 @@
     <sheet name="SERIES" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="CLUBS" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="META" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -35,7 +38,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,8 +53,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,6 +80,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -86,12 +98,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -17281,7 +17299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -17363,6 +17381,74 @@
       <c r="D3" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0012</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1967_68_0012 'KVAL  skupina A' (L25, parent=NODE_S1967_68_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0013</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1967_68_0013 'KVAL  skupina B' (L25, parent=NODE_S1967_68_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0014</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1967_68_0014 'KVAL  skupina C' (L25, parent=NODE_S1967_68_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0015</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1967_68_0015 'KVAL  skupina D' (L25, parent=NODE_S1967_68_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -54624,6 +54710,149 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0012</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1967_68_0012 'KVAL  skupina A' (L25, parent=NODE_S1967_68_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0013</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1967_68_0013 'KVAL  skupina B' (L25, parent=NODE_S1967_68_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0014</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1967_68_0014 'KVAL  skupina C' (L25, parent=NODE_S1967_68_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0015</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1967_68_0015 'KVAL  skupina D' (L25, parent=NODE_S1967_68_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S1967_68_FINAL.xlsx
+++ b/data/S1967_68_FINAL.xlsx
@@ -29,7 +29,7 @@
     <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -17299,7 +17299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -17385,14 +17385,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NODE_S1967_68_0012</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1967_68_0012 'KVAL  skupina A' (L25, parent=NODE_S1967_68_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Praha' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -17402,14 +17397,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NODE_S1967_68_0013</t>
-        </is>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1967_68_0013 'KVAL  skupina B' (L25, parent=NODE_S1967_68_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Litoměřice' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -17419,14 +17409,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NODE_S1967_68_0014</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1967_68_0014 'KVAL  skupina C' (L25, parent=NODE_S1967_68_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -17436,17 +17421,288 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NODE_S1967_68_0015</t>
-        </is>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1967_68_0015 'KVAL  skupina D' (L25, parent=NODE_S1967_68_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Trenčín' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Týnec nad Sázavou' → 'Týnec nad Labem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Svazarm Autoškola Kladno' → 'Kladno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Nová Paka' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Litomyšl' → 'Ústí nad Orlicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chvojenec' → 'Ždírec nad Doubravou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VŠ Zemědělská Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vranov nad Dyjí' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -24255,12 +24511,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Spartak Praha Sokolovo = HC Sparta Praha (Wiki D42 - registr ustavy 04/2026). Chain AC Sparta -&gt; Spartak Praha Sokolovo (1953-1965) -&gt; Sparta Praha. city Praha.</t>
+          <t>Spartak Praha Sokolovo = HC Sparta Praha (Wiki D42 - registr ustavy 04/2026). Chain AC Sparta -&gt; Spartak Praha Sokolovo (1953-1965) -&gt; Sparta Praha. city Praha. || TBD: city 'Praha' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Praha</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -24423,12 +24679,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Dukla Litoměřice (Wiki D42 - registr ustavy 04/2026). Vojensky klub - HC Stadion Litoměřice (dnes). POSTUP do 1.ligy 1961/62. city Litoměřice.</t>
+          <t>Dukla Litoměřice (Wiki D42 - registr ustavy 04/2026). Vojensky klub - HC Stadion Litoměřice (dnes). POSTUP do 1.ligy 1961/62. city Litoměřice. || TBD: city 'Litoměřice' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Litoměřice</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -24631,14 +24887,9 @@
           <t>L20</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>CLUB_S1966_67_0013</t>
-        </is>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -25063,12 +25314,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Před sezonou přejmenována z VTJ Dukla Opava na VTJ Dukla Trenčín. || TJ TTS Trenčín (TTS = Trenčianske textilní strojárne, závod). Oprava city: "TTS Trenčín" → "Trenčín". prev k overeni Pavlem. || Trenčín = HK Dukla Trenčín (Wiki - registr ustavy 04/2026). Slovensky kraj. Tradicni vojensky klub. city Trenčín.</t>
+          <t>Před sezonou přejmenována z VTJ Dukla Opava na VTJ Dukla Trenčín. || TJ TTS Trenčín (TTS = Trenčianske textilní strojárne, závod). Oprava city: "TTS Trenčín" → "Trenčín". prev k overeni Pavlem. || Trenčín = HK Dukla Trenčín (Wiki - registr ustavy 04/2026). Slovensky kraj. Tradicni vojensky klub. city Trenčín. || TBD: city 'Trenčín' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Trenčín</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -25404,12 +25655,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí.</t>
+          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí. || TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Hradec</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -26642,12 +26893,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Kolín = SC Marimex Kolín (Wiki D42 - registr ustavy 04/2026). Genealogie: Sparta Kolín -&gt; Spartak Tatra Kolín (50.leta - Tatra Kolín = podnik) -&gt; Dukla Kolín (vojensky) -&gt; SK Kolín -&gt; SC Marimex Kolín. KOL = okres Kolín. city Kolín. || Starý Kolín = Jiskra Kara Starý Kolín (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kolín). Kara = podnik. city Starý Kolín.</t>
+          <t>Kolín = SC Marimex Kolín (Wiki D42 - registr ustavy 04/2026). Genealogie: Sparta Kolín -&gt; Spartak Tatra Kolín (50.leta - Tatra Kolín = podnik) -&gt; Dukla Kolín (vojensky) -&gt; SK Kolín -&gt; SC Marimex Kolín. KOL = okres Kolín. city Kolín. || Starý Kolín = Jiskra Kara Starý Kolín (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kolín). Kara = podnik. city Starý Kolín. || TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Kara Starý Kolín</t>
+          <t>Kolín</t>
         </is>
       </c>
     </row>
@@ -27245,12 +27496,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Oprava city: „Kralupy" → „Kralupy nad Vltavou" (plný název). Smart fix prev: chybělo → 51/52 0063 (Lokomotiva Kralupy). Identity transition Lokomotiva → Železničáři (zatočená geneze, podobné jako Nymburk). || Kralupy nad Vltavou = HK Kralupy nL Vltavou (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub - Patterns: Sokol Kralupy, Spartak Kralupy. city Kralupy nad Vltavou.</t>
+          <t>Oprava city: „Kralupy" → „Kralupy nad Vltavou" (plný název). Smart fix prev: chybělo → 51/52 0063 (Lokomotiva Kralupy). Identity transition Lokomotiva → Železničáři (zatočená geneze, podobné jako Nymburk). || Kralupy nad Vltavou = HK Kralupy nL Vltavou (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub - Patterns: Sokol Kralupy, Spartak Kralupy. city Kralupy nad Vltavou. || TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Kaučuk Kralupy</t>
+          <t>Kralupy nad Vltavou</t>
         </is>
       </c>
     </row>
@@ -27371,12 +27622,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Týnec = TJ Metaz Týnec (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (Týnec nad Sázavou, okres Benesov). **Metaz** = strojírenský podnik (slévárna). city Týnec nad Sázavou.</t>
+          <t>Týnec = TJ Metaz Týnec (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (Týnec nad Sázavou, okres Benesov). **Metaz** = strojírenský podnik (slévárna). city Týnec nad Sázavou. || TBD: city 'Týnec nad Sázavou' → 'Týnec nad Labem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Týnec nad Sázavou</t>
+          <t>Týnec nad Labem</t>
         </is>
       </c>
     </row>
@@ -30206,12 +30457,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Kladno = TJ Svazarm Autoškola Kladno (Wiki D42 - registr ustavy 04/2026). **Svazarm** = Svaz pro spolupraci s armadou (vojensko-sportovni organizace). Autoskola Kladno = paralelni klub. city Kladno.</t>
+          <t>Kladno = TJ Svazarm Autoškola Kladno (Wiki D42 - registr ustavy 04/2026). **Svazarm** = Svaz pro spolupraci s armadou (vojensko-sportovni organizace). Autoskola Kladno = paralelni klub. city Kladno. || TBD: city 'Svazarm Autoškola Kladno' → 'Kladno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Svazarm Autoškola Kladno</t>
+          <t>Kladno</t>
         </is>
       </c>
     </row>
@@ -31689,12 +31940,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -31818,14 +32069,9 @@
           <t>Přebor</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>CLUB_S1966_67_0013</t>
-        </is>
-      </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -32100,14 +32346,9 @@
           <t>Soutěž</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>CLUB_S1966_67_0013</t>
-        </is>
-      </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -32515,12 +32756,12 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Cesky Krumlov). 'Sm.' = zkratka Smrcina. city Horní Planá.</t>
+          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Cesky Krumlov). 'Sm.' = zkratka Smrcina. city Horní Planá. || TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>Sm. Horní Planá</t>
+          <t>Planá</t>
         </is>
       </c>
     </row>
@@ -33455,12 +33696,12 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Stranná u Kamenice nL Lipou = TJ Sokol Stranná (Wiki D42 - registr ustavy 04/2026). Vysocina/Pelhrimovsky kraj. POZOR: hraninicni region s Jihocesko - prerodu uzemi. city Stranná u Kamenice nad Lipou.</t>
+          <t>Stranná u Kamenice nL Lipou = TJ Sokol Stranná (Wiki D42 - registr ustavy 04/2026). Vysocina/Pelhrimovsky kraj. POZOR: hraninicni region s Jihocesko - prerodu uzemi. city Stranná u Kamenice nad Lipou. || TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>Stranná u Kamenice nad Lipou</t>
+          <t>Kamenice nad Lipou</t>
         </is>
       </c>
     </row>
@@ -34135,12 +34376,12 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>Hoštice (Wiki D42 - registr ustavy 04/2026). POZOR: vícero Hostic - Stredske Hoštice (Jihocesky, okres Strakonice), Sloupne Hoštice (Jihocesky), Male Hoštice (Severomoravsky, mestska cast Opavy). 'Slovan Male Hoštice' = Severomoravsky! 'Dukla Strelske Hostice' = vojensky Strelske Hostice u Strakonic. city Hoštice.</t>
+          <t>Hoštice (Wiki D42 - registr ustavy 04/2026). POZOR: vícero Hostic - Stredske Hoštice (Jihocesky, okres Strakonice), Sloupne Hoštice (Jihocesky), Male Hoštice (Severomoravsky, mestska cast Opavy). 'Slovan Male Hoštice' = Severomoravsky! 'Dukla Strelske Hostice' = vojensky Strelske Hostice u Strakonic. city Hoštice. || TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>Slovan Malé Hoštice</t>
+          <t>Malé Hoštice</t>
         </is>
       </c>
     </row>
@@ -39232,12 +39473,12 @@
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí.</t>
+          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí. || TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>Hradec</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -40668,12 +40909,12 @@
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi.</t>
+          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi. || TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi</t>
+          <t>Rosice u Chrasti</t>
         </is>
       </c>
     </row>
@@ -42523,12 +42764,12 @@
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>Nová Paka = Jiskra/Sokol Nová Paka (Wiki D42 - registr ustavy 04/2026). Vychodocesky kraj (okres Jicin). city Nová Paka.</t>
+          <t>Nová Paka = Jiskra/Sokol Nová Paka (Wiki D42 - registr ustavy 04/2026). Vychodocesky kraj (okres Jicin). city Nová Paka. || TBD: city 'Nová Paka' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>Nová Paka</t>
+          <t>Lomnice nad Popelkou</t>
         </is>
       </c>
     </row>
@@ -42565,12 +42806,12 @@
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>Litomyšl (Wiki - registr ustavy 04/2026). Východocesky/Pardubicky kraj. Slovan Litomysl - city Litomyšl.</t>
+          <t>Litomyšl (Wiki - registr ustavy 04/2026). Východocesky/Pardubicky kraj. Slovan Litomysl - city Litomyšl. || TBD: city 'Slovan Litomyšl' → 'Ústí nad Orlicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>Slovan Litomyšl</t>
+          <t>Ústí nad Orlicí</t>
         </is>
       </c>
     </row>
@@ -42607,12 +42848,12 @@
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>Sokol Chvojenec. Almanach v zavorce „(HOL)" = district Holice (kolega misto district sloupcu zapsal do clean). || Chvojenec = Sokol Chvojenec (Wiki D42 - registr ustavy 04/2026). Vychodocesky kraj (okres Pardubice). city Chvojenec.</t>
+          <t>Sokol Chvojenec. Almanach v zavorce „(HOL)" = district Holice (kolega misto district sloupcu zapsal do clean). || Chvojenec = Sokol Chvojenec (Wiki D42 - registr ustavy 04/2026). Vychodocesky kraj (okres Pardubice). city Chvojenec. || TBD: city 'Chvojenec' → 'Ždírec nad Doubravou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>Chvojenec</t>
+          <t>Ždírec nad Doubravou</t>
         </is>
       </c>
     </row>
@@ -43487,12 +43728,12 @@
       </c>
       <c r="I456" t="inlineStr">
         <is>
-          <t>Velké Meziříčí = TJ Kablo Velké Meziříčí (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj. **Kablo** = kabelovy podnik (pobocka). city Velké Meziříčí.</t>
+          <t>Velké Meziříčí = TJ Kablo Velké Meziříčí (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj. **Kablo** = kabelovy podnik (pobocka). city Velké Meziříčí. || TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J456" t="inlineStr">
         <is>
-          <t>Kablo Velké Meziříčí</t>
+          <t>Velké Meziříčí</t>
         </is>
       </c>
     </row>
@@ -44480,12 +44721,12 @@
       </c>
       <c r="I480" t="inlineStr">
         <is>
-          <t>Brno = TJ VŠ Zemědělská Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VŠ Zemědělská** = Vysoka skola zemedelska (dnes Mendelova univerzita - MENDELU). city Brno.</t>
+          <t>Brno = TJ VŠ Zemědělská Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VŠ Zemědělská** = Vysoka skola zemedelska (dnes Mendelova univerzita - MENDELU). city Brno. || TBD: city 'VŠ Zemědělská Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J480" t="inlineStr">
         <is>
-          <t>VŠ Zemědělská Brno</t>
+          <t>Brno</t>
         </is>
       </c>
     </row>
@@ -45852,12 +46093,12 @@
       </c>
       <c r="I511" t="inlineStr">
         <is>
-          <t>Vranov nL Dyjí = TJ Rudá Hvězda Vranov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Znojmo). **Vranov nL Dyjí** = lazenske/turisticke mesto, **zámek Vranov nL Dyjí** (barokní pamatka), vodni prehrada (Vranovska prehrada - tzv. 'Moravsky moře'). RH = Ruda hvezda (SNB). NE Vranov nad Topľou (SVK)! city Vranov nad Dyjí.</t>
+          <t>Vranov nL Dyjí = TJ Rudá Hvězda Vranov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Znojmo). **Vranov nL Dyjí** = lazenske/turisticke mesto, **zámek Vranov nL Dyjí** (barokní pamatka), vodni prehrada (Vranovska prehrada - tzv. 'Moravsky moře'). RH = Ruda hvezda (SNB). NE Vranov nad Topľou (SVK)! city Vranov nad Dyjí. || TBD: city 'Vranov nad Dyjí' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J511" t="inlineStr">
         <is>
-          <t>Vranov nad Dyjí</t>
+          <t>Rudá Hvězda</t>
         </is>
       </c>
     </row>
@@ -53550,11 +53791,6 @@
           <t>CLUB_S1967_68_0028</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>CLUB_S1966_67_0013</t>
-        </is>
-      </c>
       <c r="U23" t="inlineStr">
         <is>
           <t>setrval</t>
@@ -54716,11 +54952,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -54765,21 +55001,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NODE_S1967_68_0012</t>
+          <t>CLUB_S1967_68_0019</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1967_68_0012 'KVAL  skupina A' (L25, parent=NODE_S1967_68_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Praha' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -54787,21 +55021,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NODE_S1967_68_0013</t>
+          <t>CLUB_S1967_68_0023</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1967_68_0013 'KVAL  skupina B' (L25, parent=NODE_S1967_68_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'Litoměřice' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -54809,21 +55041,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NODE_S1967_68_0014</t>
+          <t>CLUB_S1967_68_0028</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1967_68_0014 'KVAL  skupina C' (L25, parent=NODE_S1967_68_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -54831,24 +55061,482 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NODE_S1967_68_0015</t>
+          <t>CLUB_S1967_68_0038</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1967_68_0015 'KVAL  skupina D' (L25, parent=NODE_S1967_68_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'Trenčín' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S1967_68_0046</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S1967_68_0086</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S1967_68_0100</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1967_68_0103</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Týnec nad Sázavou' → 'Týnec nad Labem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1967_68_0168</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Svazarm Autoškola Kladno' → 'Kladno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1967_68_0203</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S1967_68_0206</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S1967_68_0212</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S1967_68_0221</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1967_68_0240</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1967_68_0241</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1967_68_0256</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1967_68_0317</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S1967_68_0375</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S1967_68_0403</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S1967_68_0408</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1967_68_0449</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Nová Paka' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S1967_68_0450</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovan Litomyšl' → 'Ústí nad Orlicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S1967_68_0451</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Chvojenec' → 'Ždírec nad Doubravou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S1967_68_0472</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S1967_68_0487</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S1967_68_0496</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'VŠ Zemědělská Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S1967_68_0527</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vranov nad Dyjí' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F5"/>
+  <autoFilter ref="A1:F28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -67882,11 +68570,7 @@
           <t>CLUB_S1967_68_0206</t>
         </is>
       </c>
-      <c r="R26" s="3" t="inlineStr">
-        <is>
-          <t>CLUB_S1966_67_0013</t>
-        </is>
-      </c>
+      <c r="R26" s="3" t="n"/>
       <c r="S26" s="3" t="n"/>
       <c r="T26" s="3" t="n"/>
       <c r="U26" s="3" t="n"/>
@@ -68176,11 +68860,7 @@
           <t>CLUB_S1967_68_0212</t>
         </is>
       </c>
-      <c r="R32" s="3" t="inlineStr">
-        <is>
-          <t>CLUB_S1966_67_0013</t>
-        </is>
-      </c>
+      <c r="R32" s="3" t="n"/>
       <c r="S32" s="3" t="n"/>
       <c r="T32" s="3" t="n"/>
       <c r="U32" s="3" t="n"/>
@@ -78196,6 +78876,11 @@
           <t>CLUB_S1966_67_0299</t>
         </is>
       </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>zanik</t>
+        </is>
+      </c>
       <c r="V52" t="inlineStr">
         <is>
           <t>TR_S1967_68_00242</t>

--- a/data/S1967_68_FINAL.xlsx
+++ b/data/S1967_68_FINAL.xlsx
@@ -29,7 +29,7 @@
     <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -17299,7 +17299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -17387,7 +17387,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Praha' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -17399,7 +17399,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Litoměřice' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -17411,7 +17411,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -17423,7 +17423,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Trenčín' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Svazarm Autoškola Kladno' → 'Kladno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -17435,7 +17435,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -17447,7 +17447,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -17459,7 +17459,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -17471,7 +17471,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Týnec nad Sázavou' → 'Týnec nad Labem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -17483,7 +17483,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Svazarm Autoškola Kladno' → 'Kladno' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -17495,7 +17495,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -17507,7 +17507,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -17519,7 +17519,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -17531,7 +17531,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -17543,7 +17543,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -17555,7 +17555,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -17567,142 +17567,10 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VŠ Zemědělská Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Nová Paka' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Litomyšl' → 'Ústí nad Orlicí' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chvojenec' → 'Ždírec nad Doubravou' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VŠ Zemědělská Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vranov nad Dyjí' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -17719,7 +17587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K105"/>
+  <dimension ref="A1:L105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17778,6 +17646,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17820,6 +17693,11 @@
           <t>10 týmů, jeden stůl. Mistr: Dukla Jihlava. Sestup: Chomutov (kvalifikace o I.ligu).</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17867,6 +17745,11 @@
           <t>Vítězové 4 skupin II.ligy. Dvoukolově. Top 2 do I.ligy.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -17909,6 +17792,11 @@
           <t>4 skupiny (A-D) čtyřkolově + kvalifikace o I.ligu. Pro 68/69 vzniká divize na Slovensku.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -17956,6 +17844,11 @@
           <t>Plzeň kvůli rekonstrukci měnila pořadatelství; první domácí zápas v Plzni byl bez diváků.</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17998,6 +17891,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18040,6 +17938,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18082,6 +17985,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -18124,6 +18032,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -18166,6 +18079,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -18208,6 +18126,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -18255,6 +18178,11 @@
           <t>Kvalifikace o postup do II.ligy. Sk. A: Dukla Písek postoupila, protože Motorlet B postoupit nemohl. Sk. B: Holoubkov nastoupil místo Škody Plzeň B. Sk. C: Hodonín a ZKL Brno B jako vítězové jihomoravských skupin.</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -18297,6 +18225,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -18339,6 +18272,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18381,6 +18319,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -18423,6 +18366,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -18465,6 +18413,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -18675,6 +18628,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0020</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -18717,6 +18675,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0021</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -18759,6 +18722,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0022</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -18801,6 +18769,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0023</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -18843,6 +18816,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0024</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -18885,6 +18863,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0022</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -18927,6 +18910,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0023</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -19011,6 +18999,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0022</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -19053,6 +19046,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0023</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -19268,6 +19266,11 @@
           <t>Kvalifikace o I.B třídu</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0036</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -19310,6 +19313,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0037</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -19352,6 +19360,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0038</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -19436,6 +19449,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0040</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -19478,6 +19496,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0041</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -19567,6 +19590,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0043</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -19609,6 +19637,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0044</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -19651,6 +19684,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0048</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -19871,6 +19909,11 @@
           <t>kvalifikace o I.třídu</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0052</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -19913,6 +19956,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0053</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -19955,6 +20003,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0054</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -19997,6 +20050,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0055</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -20123,6 +20181,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0058</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -20165,6 +20228,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0059</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -20207,6 +20275,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0060</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -20249,6 +20322,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0061</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -20291,6 +20369,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0062</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -20385,6 +20468,11 @@
           <t>kvalifikace o I.třídu</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0063</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -20427,6 +20515,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0064</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -20469,6 +20562,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0065</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -20511,6 +20609,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0066</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -20553,6 +20656,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0067</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -20595,6 +20703,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0068</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -20637,6 +20750,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0071</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -20679,6 +20797,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0072</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -20721,6 +20844,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0073</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -20763,6 +20891,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0074</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -20810,6 +20943,11 @@
           <t>kvalifikace o postup do KP</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0075</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -20904,6 +21042,11 @@
           <t>Kvalifikace</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0076</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -20946,6 +21089,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0077</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -20988,6 +21136,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0078</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -21030,6 +21183,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0079</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -21072,6 +21230,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0080</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -21114,6 +21277,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0081</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -21497,6 +21665,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0086</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -21539,6 +21712,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0087</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -21880,6 +22058,11 @@
           <t>Západoslovenský krajský přebor; základní část, finále a skupina o udržení.</t>
         </is>
       </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0096</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -21922,6 +22105,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0097</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -22048,6 +22236,11 @@
           <t>Středoslovenský krajský přebor; základní část, finále a skupina o udržení.</t>
         </is>
       </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0099</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -22090,6 +22283,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0097</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -22214,6 +22412,11 @@
       <c r="K105" t="inlineStr">
         <is>
           <t>Východoslovenský krajský přebor.</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0100</t>
         </is>
       </c>
     </row>
@@ -24511,12 +24714,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Spartak Praha Sokolovo = HC Sparta Praha (Wiki D42 - registr ustavy 04/2026). Chain AC Sparta -&gt; Spartak Praha Sokolovo (1953-1965) -&gt; Sparta Praha. city Praha. || TBD: city 'Praha' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Spartak Praha Sokolovo = HC Sparta Praha (Wiki D42 - registr ustavy 04/2026). Chain AC Sparta -&gt; Spartak Praha Sokolovo (1953-1965) -&gt; Sparta Praha. city Praha.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -24679,12 +24882,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Dukla Litoměřice (Wiki D42 - registr ustavy 04/2026). Vojensky klub - HC Stadion Litoměřice (dnes). POSTUP do 1.ligy 1961/62. city Litoměřice. || TBD: city 'Litoměřice' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Litoměřice (Wiki D42 - registr ustavy 04/2026). Vojensky klub - HC Stadion Litoměřice (dnes). POSTUP do 1.ligy 1961/62. city Litoměřice.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Litoměřice</t>
         </is>
       </c>
     </row>
@@ -25314,12 +25517,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Před sezonou přejmenována z VTJ Dukla Opava na VTJ Dukla Trenčín. || TJ TTS Trenčín (TTS = Trenčianske textilní strojárne, závod). Oprava city: "TTS Trenčín" → "Trenčín". prev k overeni Pavlem. || Trenčín = HK Dukla Trenčín (Wiki - registr ustavy 04/2026). Slovensky kraj. Tradicni vojensky klub. city Trenčín. || TBD: city 'Trenčín' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Před sezonou přejmenována z VTJ Dukla Opava na VTJ Dukla Trenčín. || TJ TTS Trenčín (TTS = Trenčianske textilní strojárne, závod). Oprava city: "TTS Trenčín" → "Trenčín". prev k overeni Pavlem. || Trenčín = HK Dukla Trenčín (Wiki - registr ustavy 04/2026). Slovensky kraj. Tradicni vojensky klub. city Trenčín.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>Trenčín</t>
         </is>
       </c>
     </row>
@@ -25655,12 +25858,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí. || TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Hradec nad Moravicí</t>
         </is>
       </c>
     </row>
@@ -27622,12 +27825,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Týnec = TJ Metaz Týnec (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (Týnec nad Sázavou, okres Benesov). **Metaz** = strojírenský podnik (slévárna). city Týnec nad Sázavou. || TBD: city 'Týnec nad Sázavou' → 'Týnec nad Labem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Týnec = TJ Metaz Týnec (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (Týnec nad Sázavou, okres Benesov). **Metaz** = strojírenský podnik (slévárna). city Týnec nad Sázavou.</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Týnec nad Labem</t>
+          <t>Týnec nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -39473,12 +39676,12 @@
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí. || TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí.</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Hradec nad Moravicí</t>
         </is>
       </c>
     </row>
@@ -40909,12 +41112,12 @@
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi. || TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi.</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>Rosice u Chrasti</t>
+          <t>Rosice u Chrudimi</t>
         </is>
       </c>
     </row>
@@ -42764,12 +42967,12 @@
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>Nová Paka = Jiskra/Sokol Nová Paka (Wiki D42 - registr ustavy 04/2026). Vychodocesky kraj (okres Jicin). city Nová Paka. || TBD: city 'Nová Paka' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Nová Paka = Jiskra/Sokol Nová Paka (Wiki D42 - registr ustavy 04/2026). Vychodocesky kraj (okres Jicin). city Nová Paka.</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>Lomnice nad Popelkou</t>
+          <t>Nová Paka</t>
         </is>
       </c>
     </row>
@@ -42806,12 +43009,12 @@
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>Litomyšl (Wiki - registr ustavy 04/2026). Východocesky/Pardubicky kraj. Slovan Litomysl - city Litomyšl. || TBD: city 'Slovan Litomyšl' → 'Ústí nad Orlicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Litomyšl (Wiki - registr ustavy 04/2026). Východocesky/Pardubicky kraj. Slovan Litomysl - city Litomyšl.</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>Ústí nad Orlicí</t>
+          <t>Litomyšl</t>
         </is>
       </c>
     </row>
@@ -42848,12 +43051,12 @@
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>Sokol Chvojenec. Almanach v zavorce „(HOL)" = district Holice (kolega misto district sloupcu zapsal do clean). || Chvojenec = Sokol Chvojenec (Wiki D42 - registr ustavy 04/2026). Vychodocesky kraj (okres Pardubice). city Chvojenec. || TBD: city 'Chvojenec' → 'Ždírec nad Doubravou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Sokol Chvojenec. Almanach v zavorce „(HOL)" = district Holice (kolega misto district sloupcu zapsal do clean). || Chvojenec = Sokol Chvojenec (Wiki D42 - registr ustavy 04/2026). Vychodocesky kraj (okres Pardubice). city Chvojenec.</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>Ždírec nad Doubravou</t>
+          <t>Chvojenec</t>
         </is>
       </c>
     </row>
@@ -46093,12 +46296,12 @@
       </c>
       <c r="I511" t="inlineStr">
         <is>
-          <t>Vranov nL Dyjí = TJ Rudá Hvězda Vranov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Znojmo). **Vranov nL Dyjí** = lazenske/turisticke mesto, **zámek Vranov nL Dyjí** (barokní pamatka), vodni prehrada (Vranovska prehrada - tzv. 'Moravsky moře'). RH = Ruda hvezda (SNB). NE Vranov nad Topľou (SVK)! city Vranov nad Dyjí. || TBD: city 'Vranov nad Dyjí' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Vranov nL Dyjí = TJ Rudá Hvězda Vranov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Znojmo). **Vranov nL Dyjí** = lazenske/turisticke mesto, **zámek Vranov nL Dyjí** (barokní pamatka), vodni prehrada (Vranovska prehrada - tzv. 'Moravsky moře'). RH = Ruda hvezda (SNB). NE Vranov nad Topľou (SVK)! city Vranov nad Dyjí.</t>
         </is>
       </c>
       <c r="J511" t="inlineStr">
         <is>
-          <t>Rudá Hvězda</t>
+          <t>Vranov nad Dyjí</t>
         </is>
       </c>
     </row>
@@ -54952,7 +55155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -55006,12 +55209,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1967_68_0019</t>
+          <t>CLUB_S1967_68_0028</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Praha' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55026,12 +55229,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1967_68_0023</t>
+          <t>CLUB_S1967_68_0086</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Litoměřice' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55046,12 +55249,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1967_68_0028</t>
+          <t>CLUB_S1967_68_0100</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55066,12 +55269,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1967_68_0038</t>
+          <t>CLUB_S1967_68_0168</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Trenčín' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Svazarm Autoškola Kladno' → 'Kladno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55086,12 +55289,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1967_68_0046</t>
+          <t>CLUB_S1967_68_0203</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55106,12 +55309,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1967_68_0086</t>
+          <t>CLUB_S1967_68_0206</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55126,12 +55329,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1967_68_0100</t>
+          <t>CLUB_S1967_68_0212</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55146,12 +55349,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1967_68_0103</t>
+          <t>CLUB_S1967_68_0221</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Týnec nad Sázavou' → 'Týnec nad Labem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55166,12 +55369,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1967_68_0168</t>
+          <t>CLUB_S1967_68_0240</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Svazarm Autoškola Kladno' → 'Kladno' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
     </row>
@@ -55186,12 +55389,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1967_68_0203</t>
+          <t>CLUB_S1967_68_0241</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55206,12 +55409,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1967_68_0206</t>
+          <t>CLUB_S1967_68_0256</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55226,12 +55429,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1967_68_0212</t>
+          <t>CLUB_S1967_68_0317</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -55246,12 +55449,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1967_68_0221</t>
+          <t>CLUB_S1967_68_0403</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -55266,12 +55469,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1967_68_0240</t>
+          <t>CLUB_S1967_68_0472</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+          <t>TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55286,12 +55489,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1967_68_0241</t>
+          <t>CLUB_S1967_68_0487</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -55306,237 +55509,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1967_68_0256</t>
+          <t>CLUB_S1967_68_0496</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>CLUB_S1967_68_0317</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>CLUB_S1967_68_0375</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>CLUB_S1967_68_0403</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>CLUB_S1967_68_0408</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>CLUB_S1967_68_0449</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Nová Paka' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>CLUB_S1967_68_0450</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Slovan Litomyšl' → 'Ústí nad Orlicí' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>CLUB_S1967_68_0451</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Chvojenec' → 'Ždírec nad Doubravou' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>CLUB_S1967_68_0472</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>CLUB_S1967_68_0487</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>CLUB_S1967_68_0496</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
           <t>TBD: city 'VŠ Zemědělská Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>CLUB_S1967_68_0527</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Vranov nad Dyjí' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F28"/>
+  <autoFilter ref="A1:F17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1967_68_FINAL.xlsx
+++ b/data/S1967_68_FINAL.xlsx
@@ -25090,6 +25090,11 @@
           <t>L20</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>CLUB_S1966_67_0044</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>

--- a/data/S1967_68_FINAL.xlsx
+++ b/data/S1967_68_FINAL.xlsx
@@ -17587,7 +17587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L105"/>
+  <dimension ref="A1:N105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17649,6 +17649,16 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>prev_node_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
         </is>
       </c>
     </row>

--- a/data/S1967_68_FINAL.xlsx
+++ b/data/S1967_68_FINAL.xlsx
@@ -17938,6 +17938,16 @@
           <t>NODE_S1967_68_0001</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0007</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0008</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17952,6 +17962,14 @@
         <is>
           <t>NODE_S1966_67_0006</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -17985,6 +18003,8 @@
           <t>NODE_S1967_68_0001</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17999,6 +18019,14 @@
         <is>
           <t>NODE_S1966_67_0007</t>
         </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -18032,6 +18060,8 @@
           <t>NODE_S1967_68_0001</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18046,6 +18076,14 @@
         <is>
           <t>NODE_S1966_67_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -18816,6 +18854,8 @@
           <t>NODE_S1967_68_0021</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18830,6 +18870,14 @@
         <is>
           <t>NODE_S1966_67_0024</t>
         </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -20050,6 +20098,12 @@
           <t>NODE_S1967_68_0050</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0053</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20064,6 +20118,14 @@
         <is>
           <t>NODE_S1966_67_0055</t>
         </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -20097,6 +20159,8 @@
           <t>NODE_S1967_68_0050</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20106,6 +20170,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -20139,6 +20211,8 @@
           <t>NODE_S1967_68_0050</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20148,6 +20222,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="56">
@@ -20703,6 +20785,8 @@
           <t>NODE_S1967_68_0062</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20717,6 +20801,14 @@
         <is>
           <t>NODE_S1966_67_0068</t>
         </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="68">
@@ -21277,6 +21369,8 @@
           <t>NODE_S1967_68_0074</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21291,6 +21385,14 @@
         <is>
           <t>NODE_S1966_67_0081</t>
         </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="80">
@@ -22105,6 +22207,16 @@
           <t>NODE_S1967_68_0096</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0099</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0098</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22119,6 +22231,14 @@
         <is>
           <t>NODE_S1966_67_0097</t>
         </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -22152,6 +22272,8 @@
           <t>NODE_S1967_68_0096</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22161,6 +22283,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="100">
@@ -22194,6 +22324,8 @@
           <t>NODE_S1967_68_0096</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22203,6 +22335,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="101">
@@ -22283,6 +22423,16 @@
           <t>NODE_S1967_68_0100</t>
         </is>
       </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0103</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>NODE_S1967_68_0102</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22297,6 +22447,14 @@
         <is>
           <t>NODE_S1966_67_0097</t>
         </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -22330,6 +22488,8 @@
           <t>NODE_S1967_68_0100</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22339,6 +22499,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -22372,6 +22540,8 @@
           <t>NODE_S1967_68_0100</t>
         </is>
       </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22381,6 +22551,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="105">

--- a/data/S1967_68_FINAL.xlsx
+++ b/data/S1967_68_FINAL.xlsx
@@ -714,6 +714,11 @@
           <t>Dukla Jihlava</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F4" t="n">
         <v>36</v>
       </c>
@@ -18003,8 +18008,6 @@
           <t>NODE_S1967_68_0001</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18060,8 +18063,6 @@
           <t>NODE_S1967_68_0001</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18854,8 +18855,6 @@
           <t>NODE_S1967_68_0021</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20103,7 +20102,6 @@
           <t>NODE_S1967_68_0053</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20159,8 +20157,6 @@
           <t>NODE_S1967_68_0050</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20211,8 +20207,6 @@
           <t>NODE_S1967_68_0050</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20785,8 +20779,6 @@
           <t>NODE_S1967_68_0062</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21369,8 +21361,6 @@
           <t>NODE_S1967_68_0074</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22272,8 +22262,6 @@
           <t>NODE_S1967_68_0096</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22324,8 +22312,6 @@
           <t>NODE_S1967_68_0096</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22488,8 +22474,6 @@
           <t>NODE_S1967_68_0100</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22540,8 +22524,6 @@
           <t>NODE_S1967_68_0100</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -52262,7 +52244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52478,6 +52460,18 @@
       <c r="B18" t="inlineStr">
         <is>
           <t>Plzeň kvůli rekonstrukci měnila pořadatelství; první domácí utkání v Plzni bylo bez diváků.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dukla Jihlava</t>
         </is>
       </c>
     </row>

--- a/data/S1967_68_FINAL.xlsx
+++ b/data/S1967_68_FINAL.xlsx
@@ -55977,7 +55977,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M4" t="n">
         <v>8</v>
@@ -56042,7 +56042,7 @@
         <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -56476,7 +56476,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
